--- a/july 2026/GT_JULY_26/27-07-2026/Salman ok.xlsx
+++ b/july 2026/GT_JULY_26/27-07-2026/Salman ok.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDB8DAB-A7F3-42BF-9135-0AD54DF0339C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B73B10-3F74-44E8-A05C-217405576389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -7168,7 +7168,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -7196,7 +7196,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -8575,7 +8575,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -8603,7 +8603,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -9982,7 +9982,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -10010,7 +10010,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -11387,7 +11387,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -11415,7 +11415,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -12792,7 +12792,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -12820,7 +12820,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -14209,7 +14209,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -14237,7 +14237,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -15611,7 +15611,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -15639,7 +15639,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -17013,7 +17013,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -17041,7 +17041,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -18415,7 +18415,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -18443,7 +18443,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -19817,7 +19817,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -19845,7 +19845,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -23634,7 +23634,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -23662,7 +23662,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -25036,7 +25036,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -25064,7 +25064,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -26438,7 +26438,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -26466,7 +26466,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -27840,7 +27840,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -27868,7 +27868,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -29242,7 +29242,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -29270,7 +29270,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -30644,7 +30644,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -30672,7 +30672,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -32046,7 +32046,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -32074,7 +32074,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -33448,7 +33448,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -33476,7 +33476,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -34850,7 +34850,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -34878,7 +34878,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -36252,7 +36252,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -36280,7 +36280,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -40427,7 +40427,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -40455,7 +40455,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -41829,7 +41829,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -41857,7 +41857,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -43231,7 +43231,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -43259,7 +43259,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -44633,7 +44633,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -44661,7 +44661,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -46035,7 +46035,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -46063,7 +46063,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -47434,7 +47434,7 @@
       <c r="L4" s="360"/>
       <c r="M4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="N4" s="390"/>
       <c r="O4" s="390"/>
@@ -47462,7 +47462,7 @@
       <c r="L5" s="360"/>
       <c r="M5" s="390">
         <f ca="1">M4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="N5" s="359"/>
       <c r="O5" s="359"/>
@@ -53660,7 +53660,7 @@
       <c r="G3" s="350"/>
       <c r="H3" s="347">
         <f ca="1">+'1'!N4:N4</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="I3" s="347"/>
       <c r="J3" s="348"/>
@@ -55117,7 +55117,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -55145,7 +55145,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -56531,7 +56531,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -56559,7 +56559,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -57942,7 +57942,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -57970,7 +57970,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -59355,7 +59355,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -59383,7 +59383,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -60766,7 +60766,7 @@
       <c r="M4" s="360"/>
       <c r="N4" s="390">
         <f ca="1">TODAY()+1</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -60794,7 +60794,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f ca="1">N4-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -62065,7 +62065,7 @@
     <mergeCell ref="M14:M15"/>
     <mergeCell ref="N14:N15"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
@@ -62080,7 +62080,7 @@
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0800-000003000000}">
           <x14:formula1>
             <xm:f>Summary!$B$44:$B$48</xm:f>
